--- a/doc/EnNeuro-xlsx-需求跟踪矩阵RTM-V1-1.xlsx
+++ b/doc/EnNeuro-xlsx-需求跟踪矩阵RTM-V1-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\doc\2025\面向CNN模型的深度学习框架实现和自动驾驶实践\8组\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gzs\gitHub\Enneuro-Project\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AC4DBA-4212-432F-A29A-2F36D10D1BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F76048B-12D1-45C5-9166-379B0837F1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,6 +193,14 @@
   </si>
   <si>
     <t>meter.py，Accuracy的实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅测试过CrossEntropyLoss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -608,6 +616,12 @@
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="39.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -628,6 +642,12 @@
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="47.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -648,6 +668,12 @@
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="47.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -668,6 +694,12 @@
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -688,6 +720,12 @@
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -708,6 +746,12 @@
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -728,6 +772,12 @@
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -748,6 +798,12 @@
       <c r="F10" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -767,6 +823,12 @@
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.3">
